--- a/OSBB/Data/raw/typed/Охорона.xlsx
+++ b/OSBB/Data/raw/typed/Охорона.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSBB\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\Py\OSBB\Data\raw\typed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F49FCC6-88D9-4BB8-B695-56B7CFFD42FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11950BB7-EA19-46F4-B384-6EE53E10EF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8177" yWindow="3146" windowWidth="18420" windowHeight="13560" xr2:uid="{9DC81208-272F-4EE9-B783-8EB92A88304F}"/>
+    <workbookView xWindow="8031" yWindow="2049" windowWidth="16835" windowHeight="14442" activeTab="1" xr2:uid="{9DC81208-272F-4EE9-B783-8EB92A88304F}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>квартира</t>
   </si>
@@ -204,6 +204,48 @@
   </si>
   <si>
     <t>Ш</t>
+  </si>
+  <si>
+    <t>Plate</t>
+  </si>
+  <si>
+    <t>AA12354BT</t>
+  </si>
+  <si>
+    <t>Касса</t>
+  </si>
+  <si>
+    <t>AI8756HK</t>
+  </si>
+  <si>
+    <t>BM1253BX</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>AA1178KM</t>
+  </si>
+  <si>
+    <t>KA5689BB</t>
+  </si>
+  <si>
+    <t>KA5030CI</t>
+  </si>
+  <si>
+    <t>AA3804KI</t>
+  </si>
+  <si>
+    <t>Комбинат</t>
+  </si>
+  <si>
+    <t>KA5524KA</t>
+  </si>
+  <si>
+    <t>O186</t>
+  </si>
+  <si>
+    <t>Б</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA10188-B608-4496-898F-5CE8BA620270}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.921875" bestFit="1" customWidth="1"/>
@@ -1599,12 +1641,12 @@
     <col min="5" max="6" width="10.4609375" style="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
@@ -1617,6 +1659,9 @@
       <c r="D3" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="E3" s="28" t="s">
+        <v>56</v>
+      </c>
       <c r="F3" s="28" t="s">
         <v>53</v>
       </c>
@@ -1626,8 +1671,11 @@
       <c r="H3" s="28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I3" s="28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="29">
         <v>46172</v>
       </c>
@@ -1647,7 +1695,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="29">
         <v>46173</v>
       </c>
@@ -1667,7 +1715,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="29">
         <v>46172</v>
       </c>
@@ -1684,7 +1732,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="29">
         <v>46172</v>
       </c>
@@ -1701,7 +1749,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="29">
         <v>46157</v>
       </c>
@@ -1721,7 +1769,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="29">
         <v>46157</v>
       </c>
@@ -1738,7 +1786,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="29">
         <v>46157</v>
       </c>
@@ -1749,7 +1797,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="29">
         <v>46164</v>
       </c>
@@ -1769,7 +1817,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="29">
         <v>46163</v>
       </c>
@@ -1786,7 +1834,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="29">
         <v>46163</v>
       </c>
@@ -1806,7 +1854,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="29">
         <v>46163</v>
       </c>
@@ -1823,7 +1871,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="29">
         <v>46163</v>
       </c>
@@ -1840,7 +1888,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1935,70 +1983,334 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="29"/>
+      <c r="A21" s="29">
+        <v>46165</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>54</v>
+      </c>
       <c r="G21">
-        <f>SUM(G4:G20)</f>
-        <v>15750</v>
-      </c>
-      <c r="H21">
+        <v>1000</v>
+      </c>
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="29">
+        <v>46172</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22">
+        <v>800</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="29">
+        <v>46173</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>500</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="29">
+        <v>46167</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
+        <v>150</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="29">
+        <v>46172</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25">
+        <v>500</v>
+      </c>
+      <c r="I25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="29">
+        <v>46172</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>500</v>
+      </c>
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27">
+        <v>500</v>
+      </c>
+      <c r="I27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E28" s="28">
+        <v>8092</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28">
+        <v>500</v>
+      </c>
+      <c r="I28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="29">
+        <v>46174</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29">
+        <v>2000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30">
+        <v>500</v>
+      </c>
+      <c r="I30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31">
+        <v>500</v>
+      </c>
+      <c r="I31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E32" s="28">
+        <v>9000</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32">
+        <v>300</v>
+      </c>
+      <c r="I32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E33" s="28">
+        <v>5003</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33">
+        <v>500</v>
+      </c>
+      <c r="I33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="29">
+        <v>46174</v>
+      </c>
+      <c r="E34" s="28">
+        <v>9868</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34">
+        <v>500</v>
+      </c>
+      <c r="I34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A35" s="29">
+        <v>46174</v>
+      </c>
+      <c r="C35">
+        <v>132</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35">
+        <v>400</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" s="29"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" s="29"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A38" s="29"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" s="29"/>
+      <c r="G39">
+        <f>SUM(G4:G24)</f>
+        <v>18200</v>
+      </c>
+      <c r="H39">
         <f>SUM(H4:H19)</f>
         <v>1350</v>
       </c>
-      <c r="I21">
-        <f>G21-H21</f>
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="29"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B23" s="30" t="s">
+      <c r="I39">
+        <f>G39-H39</f>
+        <v>16850</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A40" s="29"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B41" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="G23">
+      <c r="G41">
         <v>7900</v>
       </c>
-      <c r="H23">
+      <c r="H41">
         <v>6600</v>
       </c>
-      <c r="I23">
+      <c r="I41">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B24" s="30" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B42" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G24">
+      <c r="G42">
         <v>11500</v>
       </c>
-      <c r="H24">
+      <c r="H42">
         <v>11000</v>
       </c>
-      <c r="I24">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B25" s="30" t="s">
+      <c r="I42">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B43" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G25">
+      <c r="G43">
         <v>6750</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G26">
-        <f>SUM(G23:G25)</f>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G44">
+        <f>SUM(G41:G43)</f>
         <v>26150</v>
       </c>
-      <c r="H26">
-        <f>SUM(H23:H24)</f>
+      <c r="H44">
+        <f>SUM(H41:H42)</f>
         <v>17600</v>
       </c>
-      <c r="I26">
-        <f xml:space="preserve"> G26-H26</f>
+      <c r="I44">
+        <f xml:space="preserve"> G44-H44</f>
         <v>8550</v>
       </c>
     </row>
